--- a/data/financial_projections_24m.xlsx
+++ b/data/financial_projections_24m.xlsx
@@ -625,7 +625,7 @@
     <row r="6" ht="30" customHeight="1" s="25">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Vehicle disposal trigger</t>
+          <t>Contract length</t>
         </is>
       </c>
       <c r="B6" s="18" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>car trigger for the disposal (with no disposal revenue) of all vehicles.</t>
+          <t>Client contract length that doubles as trigger for the disposal (with no disposal revenue) of all vehicles.</t>
         </is>
       </c>
     </row>
